--- a/output/supplementary/P1_J4_by_pathway.xlsx
+++ b/output/supplementary/P1_J4_by_pathway.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.971055088702148</v>
+        <v>2.96551724137931</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.151338939252095</v>
+        <v>3.151007322046774</v>
       </c>
       <c r="E2" t="n">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="3">
@@ -469,53 +469,34 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
       <c r="D3" t="n">
-        <v>2.64575131106459</v>
+        <v>3.020761493398644</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>PMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1.832250762625809</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PMA</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.832250762625809</v>
-      </c>
-      <c r="E5" t="n">
         <v>8</v>
       </c>
     </row>
